--- a/配置文档/GoodsConfig.xlsx
+++ b/配置文档/GoodsConfig.xlsx
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>解锁VIP</t>
+          <t>Unlock VIP</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>新手优惠5折钻石包</t>
+          <t>Starter Diamond Pack (50% Off)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>小额钻石包</t>
+          <t>Small Diamond Pack</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>中额钻石包</t>
+          <t>Medium Diamond Pack</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>获得1698颗钻石</t>
+          <t>Large Diamond Pack</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>小周卡X1</t>
+          <t>Small Weekly Diamond Pass x1</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>大周卡X1</t>
+          <t>Large Weekly Diamond Pass x1</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>发送一次钻石红包</t>
+          <t>Send a Diamond Red Packet</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">

--- a/配置文档/GoodsConfig.xlsx
+++ b/配置文档/GoodsConfig.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>解锁VIP</t>
+          <t>Unlock VIP.</t>
         </is>
       </c>
       <c r="E5" s="21" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>获得48颗钻石(超值!)</t>
+          <t>Get 48 Diamonds. Great value!</t>
         </is>
       </c>
       <c r="E6" s="21" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>获得152颗钻石</t>
+          <t>Get 152 Diamonds.</t>
         </is>
       </c>
       <c r="E7" s="21" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>获得618颗钻石</t>
+          <t>Get 618 Diamonds.</t>
         </is>
       </c>
       <c r="E8" s="21" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>获得1698颗钻石</t>
+          <t>Get 1,698 Diamonds.</t>
         </is>
       </c>
       <c r="E9" s="21" t="n">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>Small Weekly Diamond Pass x1</t>
+          <t>Small Weekly Diamond Pass × 1</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>立即获得108钻石,每天签到多获得12钻石(6天)</t>
+          <t>Get 108 Diamonds instantly, plus 12 bonus Diamonds each day you check in for the next 6 days.</t>
         </is>
       </c>
       <c r="E11" s="21" t="n">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Large Weekly Diamond Pass x1</t>
+          <t>Large Weekly Diamond Pass × 1</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>立即获得400钻石,每天签到多获得63钻石(6天)</t>
+          <t>Get 400 Diamonds instantly, plus 63 bonus Diamonds each day you check in for the next 6 days.</t>
         </is>
       </c>
       <c r="E12" s="21" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>发送一次钻石红包</t>
+          <t>Send a Diamond Red Packet.</t>
         </is>
       </c>
       <c r="E13" s="21" t="n">
@@ -3232,7 +3232,7 @@
       <s:c r="C6" s="21" t="n"/>
       <s:c r="D6" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X2</s:t>
+          <s:t>Training Multiplier × 2</s:t>
         </s:is>
       </s:c>
       <s:c r="E6" s="21" t="n">
@@ -3251,7 +3251,7 @@
       <s:c r="C7" s="21" t="n"/>
       <s:c r="D7" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X4</s:t>
+          <s:t>Training Multiplier × 4</s:t>
         </s:is>
       </s:c>
       <s:c r="E7" s="21" t="n">
@@ -3270,7 +3270,7 @@
       <s:c r="C8" s="21" t="n"/>
       <s:c r="D8" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X8</s:t>
+          <s:t>Training Multiplier × 8</s:t>
         </s:is>
       </s:c>
       <s:c r="E8" s="21" t="n">
@@ -3289,7 +3289,7 @@
       <s:c r="C9" s="21" t="n"/>
       <s:c r="D9" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X16</s:t>
+          <s:t>Training Multiplier × 16</s:t>
         </s:is>
       </s:c>
       <s:c r="E9" s="21" t="n">
@@ -3308,7 +3308,7 @@
       <s:c r="C10" s="21" t="n"/>
       <s:c r="D10" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X32</s:t>
+          <s:t>Training Multiplier × 32</s:t>
         </s:is>
       </s:c>
       <s:c r="E10" s="21" t="n">
@@ -3327,7 +3327,7 @@
       <s:c r="C11" s="21" t="n"/>
       <s:c r="D11" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X64</s:t>
+          <s:t>Training Multiplier × 64</s:t>
         </s:is>
       </s:c>
       <s:c r="E11" s="21" t="n">
@@ -3346,7 +3346,7 @@
       <s:c r="C12" s="21" t="n"/>
       <s:c r="D12" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X128</s:t>
+          <s:t>Training Multiplier × 128</s:t>
         </s:is>
       </s:c>
       <s:c r="E12" s="21" t="n">
@@ -3365,7 +3365,7 @@
       <s:c r="C13" s="21" t="n"/>
       <s:c r="D13" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X256</s:t>
+          <s:t>Training Multiplier × 256</s:t>
         </s:is>
       </s:c>
       <s:c r="E13" s="21" t="n">
@@ -3384,7 +3384,7 @@
       <s:c r="C14" s="21" t="n"/>
       <s:c r="D14" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X512</s:t>
+          <s:t>Training Multiplier × 512</s:t>
         </s:is>
       </s:c>
       <s:c r="E14" s="21" t="n">
@@ -3403,7 +3403,7 @@
       <s:c r="C15" s="21" t="n"/>
       <s:c r="D15" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X1024</s:t>
+          <s:t>Training Multiplier × 1024</s:t>
         </s:is>
       </s:c>
       <s:c r="E15" s="21" t="n">
@@ -3422,7 +3422,7 @@
       <s:c r="C16" s="21" t="n"/>
       <s:c r="D16" s="21" t="inlineStr">
         <s:is>
-          <s:t>训练倍率X2048</s:t>
+          <s:t>Training Multiplier × 2048</s:t>
         </s:is>
       </s:c>
       <s:c r="E16" s="21" t="n">
@@ -3441,7 +3441,7 @@
       <s:c r="C21" s="21" t="n"/>
       <s:c r="D21" s="21" t="inlineStr">
         <s:is>
-          <s:t>扩容背包格子+1</s:t>
+          <s:t>Backpack Capacity +1</s:t>
         </s:is>
       </s:c>
       <s:c r="E21" s="21" t="n">
@@ -3463,7 +3463,7 @@
       <s:c r="C22" s="21" t="n"/>
       <s:c r="D22" s="21" t="inlineStr">
         <s:is>
-          <s:t>扩容背包格子+1</s:t>
+          <s:t>Backpack Capacity +1</s:t>
         </s:is>
       </s:c>
       <s:c r="E22" s="21" t="n">
@@ -3485,7 +3485,7 @@
       <s:c r="C23" s="21" t="n"/>
       <s:c r="D23" s="21" t="inlineStr">
         <s:is>
-          <s:t>扩容背包格子+1</s:t>
+          <s:t>Backpack Capacity +1</s:t>
         </s:is>
       </s:c>
       <s:c r="E23" s="21" t="n">
@@ -3507,7 +3507,7 @@
       <s:c r="C25" s="21" t="n"/>
       <s:c r="D25" s="21" t="inlineStr">
         <s:is>
-          <s:t>小训练力量包</s:t>
+          <s:t>Small Strength Pack</s:t>
         </s:is>
       </s:c>
       <s:c r="E25" s="21" t="n">
@@ -3529,7 +3529,7 @@
       <s:c r="C26" s="21" t="n"/>
       <s:c r="D26" s="21" t="inlineStr">
         <s:is>
-          <s:t>中训练力量包</s:t>
+          <s:t>Medium Strength Pack</s:t>
         </s:is>
       </s:c>
       <s:c r="E26" s="21" t="n">
@@ -3551,7 +3551,7 @@
       <s:c r="C27" s="21" t="n"/>
       <s:c r="D27" s="21" t="inlineStr">
         <s:is>
-          <s:t>大训练力量包</s:t>
+          <s:t>Large Strength Pack</s:t>
         </s:is>
       </s:c>
       <s:c r="E27" s="21" t="n">
@@ -3573,7 +3573,7 @@
       <s:c r="C29" s="21" t="n"/>
       <s:c r="D29" s="21" t="inlineStr">
         <s:is>
-          <s:t>双倍出售</s:t>
+          <s:t>Double Sell Value</s:t>
         </s:is>
       </s:c>
       <s:c r="E29" s="21" t="n">

--- a/配置文档/GoodsConfig.xlsx
+++ b/配置文档/GoodsConfig.xlsx
@@ -1608,23 +1608,23 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Starter Diamond Pack (50% Off)</t>
+          <t>Starter Diamond Pack (67折)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Get 48 Diamonds. Great value!</t>
+          <t>Get 84 Diamonds. Great value!</t>
         </is>
       </c>
       <c r="E6" s="21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F6" s="23" t="n"/>
       <c r="G6" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -1814,12 +1814,12 @@
         </is>
       </c>
       <c r="E14" s="21" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F14" s="23" t="n"/>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>MinRebirth=0,MaxRebirth=2</t>
+          <t>MinRebirth=0,MaxRebirth=4</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -1848,12 +1848,12 @@
         </is>
       </c>
       <c r="E15" s="21" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F15" s="21" t="n"/>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>MinRebirth=3,MaxRebirth=5</t>
+          <t>MinRebirth=5,MaxRebirth=9</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -1882,12 +1882,12 @@
         </is>
       </c>
       <c r="E16" s="21" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F16" s="23" t="n"/>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>MinRebirth=6,MaxRebirth=8</t>
+          <t>MinRebirth=10,MaxRebirth=14</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -1916,12 +1916,12 @@
         </is>
       </c>
       <c r="E17" s="21" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F17" s="21" t="n"/>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>MinRebirth=9,MaxRebirth=10</t>
+          <t>MinRebirth=15,MaxRebirth=19</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -1931,13 +1931,91 @@
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="23" t="n"/>
+      <c r="A18" s="21" t="n">
+        <v>405</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>SkipRebirth</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Skip Rebirth</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Skip the level requirement and rebirth once.</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="F18" s="21" t="n"/>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>MinRebirth=20,MaxRebirth=24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="D19" s="23" t="n"/>
+      <c r="A19" s="21" t="n">
+        <v>406</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>SkipRebirth</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Skip Rebirth</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Skip the level requirement and rebirth once.</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>118</v>
+      </c>
+      <c r="F19" s="21" t="n"/>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>MinRebirth=25,MaxRebirth=29</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="D20" s="23" t="n"/>
+      <c r="A20" s="21" t="n">
+        <v>407</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>SkipRebirth</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Skip Rebirth</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Skip the level requirement and rebirth once.</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>198</v>
+      </c>
+      <c r="F20" s="21" t="n"/>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>MinRebirth=30,MaxRebirth=35</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="D21" s="23" t="n"/>
